--- a/プロジェクト型演習_成果ドキュメント_メニュー.xlsx
+++ b/プロジェクト型演習_成果ドキュメント_メニュー.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER124\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\project-based-learning\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FABE7BB-0800-4306-9D39-F8D1B675E65C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB21A2CE-BDA8-4874-994A-141CB6870C21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="10455" windowHeight="10905" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="10455" windowHeight="10905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="93">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -314,65 +314,9 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>ユーザがメニュー画面を閲覧する。</t>
-    <rPh sb="8" eb="10">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>エツラン</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>ユーザがログイン状態であること。</t>
     <rPh sb="8" eb="10">
       <t>ジョウタイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>基本フロー1：未ログイン状態であった場合。
-1. 「ログイン画面」へ遷移する。</t>
-    <rPh sb="0" eb="2">
-      <t>キホン</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>バアイ</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="34" eb="36">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>1. ユーザがログイン状態で「メニュー画面」へ遷移する。</t>
-    <rPh sb="11" eb="13">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>「メニュー画面」へ遷移する。</t>
-    <rPh sb="5" eb="7">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -385,20 +329,225 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>ViewServletに送る。</t>
-    <rPh sb="12" eb="13">
-      <t>オク</t>
+    <t>ユーザがメニュー画面から「タスク登録画面」「タスク一覧表示画面」「ログアウト画面」のいずれかへ遷移する。</t>
+    <rPh sb="8" eb="10">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="16" eb="20">
+      <t>トウロクガメン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="27" eb="31">
+      <t>ヒョウジガメン</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>センイ</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>ログアウト画面へ遷移。</t>
+    <t>基本フロー1-1、2-1：未ログイン状態であった場合。
+1. 「ログイン画面」へ遷移する。</t>
+    <rPh sb="0" eb="2">
+      <t>キホン</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスクを登録したい場合。
+1-1. ユーザがログイン状態で「メニュー画面」の「タスクを登録」ボタンを押下する。
+1-2. システムが画面を「メニュー画面」から「タスク登録画面」へ遷移させる。
+タスク一覧を確認したい場合。
+2-1. ユーザがログイン状態で「メニュー画面」の「タスク一覧を表示」ボタンを押下する。
+2-2. システムが画面を「メニュー画面」から「タスク一覧表示画面」へ遷移させる。
+ログアウトしたい場合。
+3-1. ユーザがログイン状態で「メニュー画面」の「ログアウト」ボタンを押下する。
+3-2. システムが画面を「メニュー画面」から「ログアウト画面」へ遷移させる。</t>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="43" eb="45">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="83" eb="85">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="100" eb="102">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="103" eb="105">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="108" eb="110">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="125" eb="127">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="133" eb="135">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="141" eb="143">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="144" eb="146">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="151" eb="153">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="167" eb="169">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="175" eb="177">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="184" eb="190">
+      <t>イチランヒョウジガメン</t>
+    </rPh>
+    <rPh sb="192" eb="194">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="208" eb="210">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="225" eb="227">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="233" eb="235">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="248" eb="250">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="264" eb="266">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="272" eb="274">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="283" eb="285">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="287" eb="289">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスクを登録したい場合：「タスク登録画面」へ遷移する。
+タスク一覧を確認したい場合：「タスク一覧表示画面」へ遷移する。
+ログアウトしたい場合：「ログアウト画面」へ遷移する。</t>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="39" eb="41">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="48" eb="52">
+      <t>ヒョウジガメン</t>
+    </rPh>
+    <rPh sb="54" eb="56">
+      <t>センイ</t>
+    </rPh>
+    <rPh sb="68" eb="70">
+      <t>バアイ</t>
+    </rPh>
+    <rPh sb="77" eb="79">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="81" eb="83">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスクを登録</t>
+    <rPh sb="4" eb="6">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>"タスクを登録"</t>
     <rPh sb="5" eb="7">
-      <t>ガメン</t>
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>タスク登録画面へ遷移。</t>
+    <rPh sb="3" eb="7">
+      <t>トウロクガメン</t>
     </rPh>
     <rPh sb="8" eb="10">
       <t>センイ</t>
     </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ViewServletに送り、タスク一覧表示画面へ遷移。</t>
+    <rPh sb="12" eb="13">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="18" eb="24">
+      <t>イチランヒョウジガメン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>LogoutServletへ送り、ログアウト画面へ遷移。</t>
+    <rPh sb="14" eb="15">
+      <t>オク</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>taskRegister.jsp</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1411,7 +1560,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1547,263 +1696,287 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="63" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2717,15 +2890,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1042223</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>228073</xdr:rowOff>
+      <xdr:colOff>1026860</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>12992</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>146537</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>218548</xdr:rowOff>
+      <xdr:colOff>131174</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>3467</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2740,8 +2913,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3187965" y="2300546"/>
-          <a:ext cx="1323325" cy="252150"/>
+          <a:off x="3162304" y="2609323"/>
+          <a:ext cx="1347297" cy="251644"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2849,15 +3022,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>629812</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>92473</xdr:rowOff>
+      <xdr:colOff>614449</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>138561</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1042223</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>94724</xdr:rowOff>
+      <xdr:colOff>1026860</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>140812</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2874,7 +3047,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="2775554" y="2426621"/>
+          <a:off x="2749893" y="2734892"/>
           <a:ext cx="412411" cy="2251"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -2902,15 +3075,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>360151</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>223459</xdr:rowOff>
+      <xdr:colOff>344788</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>8378</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>644127</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>236712</xdr:rowOff>
+      <xdr:colOff>628764</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>21631</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2925,8 +3098,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2501960" y="2296857"/>
-          <a:ext cx="283976" cy="281637"/>
+          <a:off x="2480232" y="2604709"/>
+          <a:ext cx="283976" cy="274422"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2956,7 +3129,7 @@
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>①</a:t>
+            <a:t>②</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
         </a:p>
@@ -2967,15 +3140,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1047485</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>201761</xdr:rowOff>
+      <xdr:colOff>1032122</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>155673</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>826200</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>192236</xdr:rowOff>
+      <xdr:colOff>810837</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>146148</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2990,8 +3163,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3189294" y="2811927"/>
-          <a:ext cx="894351" cy="258859"/>
+          <a:off x="3167566" y="3013173"/>
+          <a:ext cx="900206" cy="251644"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3044,15 +3217,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>635074</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>62807</xdr:rowOff>
+      <xdr:colOff>619711</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>16719</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1047485</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>68412</xdr:rowOff>
+      <xdr:colOff>1032122</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>22324</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -3069,7 +3242,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="2776883" y="2941357"/>
+          <a:off x="2755155" y="3135388"/>
           <a:ext cx="412411" cy="5605"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -3097,15 +3270,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>365413</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>197147</xdr:rowOff>
+      <xdr:colOff>350050</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>151059</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>649389</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>210400</xdr:rowOff>
+      <xdr:colOff>634026</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>164312</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3120,8 +3293,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2507222" y="2807313"/>
-          <a:ext cx="283976" cy="281637"/>
+          <a:off x="2485494" y="3008559"/>
+          <a:ext cx="283976" cy="274422"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3151,7 +3324,202 @@
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>②</a:t>
+            <a:t>③</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1033226</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>135301</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1008898</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>125776</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D13AD499-86A0-4B3D-B1D4-41F98A0AEC75}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3182617" y="2209495"/>
+          <a:ext cx="1091100" cy="259932"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>タスクを登録</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>620814</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>265267</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1033226</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1952</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="6" name="直線コネクタ 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02432B6D-3B6B-496E-93EC-C7CEC3CE3EAE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="3" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="2770205" y="2339461"/>
+          <a:ext cx="412412" cy="6142"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="19050"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>351153</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>130687</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>635129</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>143940</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="テキスト ボックス 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE8F4663-838E-4176-8AD1-33AD0D4930EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2486597" y="2204679"/>
+          <a:ext cx="283976" cy="274422"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>①</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
         </a:p>
@@ -3369,85 +3737,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="79" t="s">
+      <c r="C2" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
-      <c r="I2" s="80"/>
-      <c r="J2" s="80"/>
-      <c r="K2" s="80"/>
-      <c r="L2" s="80"/>
-      <c r="M2" s="80"/>
-      <c r="N2" s="80"/>
-      <c r="O2" s="80"/>
+      <c r="D2" s="86"/>
+      <c r="E2" s="86"/>
+      <c r="F2" s="86"/>
+      <c r="G2" s="86"/>
+      <c r="H2" s="86"/>
+      <c r="I2" s="86"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="86"/>
+      <c r="M2" s="86"/>
+      <c r="N2" s="86"/>
+      <c r="O2" s="86"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="60"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="60"/>
-      <c r="K3" s="60"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="60"/>
-      <c r="N3" s="60"/>
-      <c r="O3" s="60"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="61"/>
+      <c r="G3" s="61"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="61"/>
+      <c r="L3" s="61"/>
+      <c r="M3" s="61"/>
+      <c r="N3" s="61"/>
+      <c r="O3" s="61"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="60"/>
-      <c r="D4" s="60"/>
-      <c r="E4" s="60"/>
-      <c r="F4" s="60"/>
-      <c r="G4" s="60"/>
-      <c r="H4" s="60"/>
-      <c r="I4" s="60"/>
-      <c r="J4" s="60"/>
-      <c r="K4" s="60"/>
-      <c r="L4" s="60"/>
-      <c r="M4" s="60"/>
-      <c r="N4" s="60"/>
-      <c r="O4" s="60"/>
+      <c r="C4" s="61"/>
+      <c r="D4" s="61"/>
+      <c r="E4" s="61"/>
+      <c r="F4" s="61"/>
+      <c r="G4" s="61"/>
+      <c r="H4" s="61"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="61"/>
+      <c r="K4" s="61"/>
+      <c r="L4" s="61"/>
+      <c r="M4" s="61"/>
+      <c r="N4" s="61"/>
+      <c r="O4" s="61"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="60"/>
-      <c r="D5" s="60"/>
-      <c r="E5" s="60"/>
-      <c r="F5" s="60"/>
-      <c r="G5" s="60"/>
-      <c r="H5" s="60"/>
-      <c r="I5" s="60"/>
-      <c r="J5" s="60"/>
-      <c r="K5" s="60"/>
-      <c r="L5" s="60"/>
-      <c r="M5" s="60"/>
-      <c r="N5" s="60"/>
-      <c r="O5" s="60"/>
+      <c r="C5" s="61"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="61"/>
+      <c r="H5" s="61"/>
+      <c r="I5" s="61"/>
+      <c r="J5" s="61"/>
+      <c r="K5" s="61"/>
+      <c r="L5" s="61"/>
+      <c r="M5" s="61"/>
+      <c r="N5" s="61"/>
+      <c r="O5" s="61"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="60"/>
-      <c r="D6" s="60"/>
-      <c r="E6" s="60"/>
-      <c r="F6" s="60"/>
-      <c r="G6" s="60"/>
-      <c r="H6" s="60"/>
-      <c r="I6" s="60"/>
-      <c r="J6" s="60"/>
-      <c r="K6" s="60"/>
-      <c r="L6" s="60"/>
-      <c r="M6" s="60"/>
-      <c r="N6" s="60"/>
-      <c r="O6" s="60"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
+      <c r="I6" s="61"/>
+      <c r="J6" s="61"/>
+      <c r="K6" s="61"/>
+      <c r="L6" s="61"/>
+      <c r="M6" s="61"/>
+      <c r="N6" s="61"/>
+      <c r="O6" s="61"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -3467,46 +3835,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="81" t="s">
+      <c r="E8" s="87" t="s">
         <v>66</v>
       </c>
-      <c r="F8" s="60"/>
-      <c r="G8" s="60"/>
-      <c r="H8" s="60"/>
-      <c r="I8" s="60"/>
-      <c r="J8" s="60"/>
-      <c r="K8" s="60"/>
-      <c r="L8" s="60"/>
-      <c r="M8" s="60"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="61"/>
+      <c r="M8" s="61"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="77" t="s">
+      <c r="G13" s="83" t="s">
         <v>1</v>
       </c>
-      <c r="H13" s="48"/>
-      <c r="I13" s="82">
+      <c r="H13" s="70"/>
+      <c r="I13" s="88">
         <v>46230</v>
       </c>
-      <c r="J13" s="46"/>
-      <c r="K13" s="48"/>
+      <c r="J13" s="69"/>
+      <c r="K13" s="70"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="77"/>
-      <c r="H14" s="48"/>
-      <c r="I14" s="77"/>
-      <c r="J14" s="46"/>
-      <c r="K14" s="48"/>
+      <c r="G14" s="83"/>
+      <c r="H14" s="70"/>
+      <c r="I14" s="83"/>
+      <c r="J14" s="69"/>
+      <c r="K14" s="70"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="77"/>
-      <c r="H15" s="48"/>
-      <c r="I15" s="77"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="48"/>
+      <c r="G15" s="83"/>
+      <c r="H15" s="70"/>
+      <c r="I15" s="83"/>
+      <c r="J15" s="69"/>
+      <c r="K15" s="70"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -3515,13 +3883,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="78" t="s">
+      <c r="G17" s="84" t="s">
         <v>64</v>
       </c>
-      <c r="H17" s="60"/>
-      <c r="I17" s="60"/>
-      <c r="J17" s="60"/>
-      <c r="K17" s="60"/>
+      <c r="H17" s="61"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="61"/>
+      <c r="K17" s="61"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -4535,19 +4903,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="52" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="51"/>
-      <c r="F1" s="52" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="51"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
@@ -4559,194 +4927,194 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="63" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="64"/>
-      <c r="F2" s="63" t="s">
+      <c r="E2" s="49"/>
+      <c r="F2" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="64"/>
-      <c r="H2" s="69">
+      <c r="G2" s="49"/>
+      <c r="H2" s="52">
         <v>46231</v>
       </c>
-      <c r="I2" s="71" t="s">
+      <c r="I2" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="J2" s="72"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="73"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="56"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="89"/>
-      <c r="B4" s="90"/>
-      <c r="C4" s="91"/>
-      <c r="D4" s="92"/>
-      <c r="E4" s="91"/>
-      <c r="F4" s="92"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="84"/>
+      <c r="A4" s="108"/>
+      <c r="B4" s="109"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="102"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="85" t="s">
+      <c r="A5" s="103" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="86" t="s">
+      <c r="B5" s="104"/>
+      <c r="C5" s="66"/>
+      <c r="D5" s="105" t="s">
         <v>75</v>
       </c>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="56"/>
+      <c r="E5" s="104"/>
+      <c r="F5" s="104"/>
+      <c r="G5" s="104"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="106"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="87" t="s">
+      <c r="A6" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="46"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="45" t="s">
+      <c r="B6" s="69"/>
+      <c r="C6" s="70"/>
+      <c r="D6" s="80" t="s">
+        <v>83</v>
+      </c>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="91"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="89" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="69"/>
+      <c r="C7" s="70"/>
+      <c r="D7" s="80" t="s">
+        <v>67</v>
+      </c>
+      <c r="E7" s="69"/>
+      <c r="F7" s="69"/>
+      <c r="G7" s="69"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="69"/>
+      <c r="J7" s="91"/>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A8" s="89" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="69"/>
+      <c r="C8" s="70"/>
+      <c r="D8" s="80" t="s">
         <v>80</v>
       </c>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
-      <c r="J6" s="47"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="87" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="46"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="45" t="s">
-        <v>67</v>
-      </c>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="46"/>
-      <c r="J7" s="47"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="87" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" s="46"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="46"/>
-      <c r="J8" s="47"/>
-    </row>
-    <row r="9" spans="1:10" ht="87.75" customHeight="1">
-      <c r="A9" s="95" t="s">
+      <c r="E8" s="69"/>
+      <c r="F8" s="69"/>
+      <c r="G8" s="69"/>
+      <c r="H8" s="69"/>
+      <c r="I8" s="69"/>
+      <c r="J8" s="91"/>
+    </row>
+    <row r="9" spans="1:10" ht="164.25" customHeight="1">
+      <c r="A9" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="98" t="s">
+      <c r="B9" s="100" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="48"/>
-      <c r="D9" s="93" t="s">
-        <v>83</v>
-      </c>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="46"/>
-      <c r="J9" s="47"/>
-    </row>
-    <row r="10" spans="1:10" ht="100.5" customHeight="1">
-      <c r="A10" s="96"/>
-      <c r="B10" s="98" t="s">
+      <c r="C9" s="70"/>
+      <c r="D9" s="90" t="s">
+        <v>85</v>
+      </c>
+      <c r="E9" s="69"/>
+      <c r="F9" s="69"/>
+      <c r="G9" s="69"/>
+      <c r="H9" s="69"/>
+      <c r="I9" s="69"/>
+      <c r="J9" s="91"/>
+    </row>
+    <row r="10" spans="1:10" ht="48.75" customHeight="1">
+      <c r="A10" s="98"/>
+      <c r="B10" s="100" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="48"/>
-      <c r="D10" s="93" t="s">
+      <c r="C10" s="70"/>
+      <c r="D10" s="90" t="s">
         <v>68</v>
       </c>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="47"/>
+      <c r="E10" s="69"/>
+      <c r="F10" s="69"/>
+      <c r="G10" s="69"/>
+      <c r="H10" s="69"/>
+      <c r="I10" s="69"/>
+      <c r="J10" s="91"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="97"/>
-      <c r="B11" s="98" t="s">
+      <c r="A11" s="99"/>
+      <c r="B11" s="100" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="48"/>
-      <c r="D11" s="93" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="47"/>
-    </row>
-    <row r="12" spans="1:10" ht="34.5" customHeight="1">
-      <c r="A12" s="87" t="s">
+      <c r="C11" s="70"/>
+      <c r="D11" s="90" t="s">
+        <v>84</v>
+      </c>
+      <c r="E11" s="69"/>
+      <c r="F11" s="69"/>
+      <c r="G11" s="69"/>
+      <c r="H11" s="69"/>
+      <c r="I11" s="69"/>
+      <c r="J11" s="91"/>
+    </row>
+    <row r="12" spans="1:10" ht="57.75" customHeight="1">
+      <c r="A12" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="B12" s="46"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="93" t="s">
-        <v>84</v>
-      </c>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="47"/>
+      <c r="B12" s="69"/>
+      <c r="C12" s="70"/>
+      <c r="D12" s="90" t="s">
+        <v>86</v>
+      </c>
+      <c r="E12" s="69"/>
+      <c r="F12" s="69"/>
+      <c r="G12" s="69"/>
+      <c r="H12" s="69"/>
+      <c r="I12" s="69"/>
+      <c r="J12" s="91"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A13" s="94" t="s">
+      <c r="A13" s="92" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="53"/>
-      <c r="C13" s="54"/>
-      <c r="D13" s="67" t="s">
+      <c r="B13" s="93"/>
+      <c r="C13" s="94"/>
+      <c r="D13" s="95" t="s">
         <v>68</v>
       </c>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="53"/>
-      <c r="J13" s="68"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
+      <c r="H13" s="93"/>
+      <c r="I13" s="93"/>
+      <c r="J13" s="96"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -5737,6 +6105,18 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
     <mergeCell ref="A12:C12"/>
     <mergeCell ref="D12:J12"/>
     <mergeCell ref="A13:C13"/>
@@ -5752,18 +6132,6 @@
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -5782,19 +6150,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="52" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="51"/>
-      <c r="F1" s="52" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="51"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -5806,48 +6174,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="63" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="64"/>
-      <c r="F2" s="63" t="s">
+      <c r="E2" s="49"/>
+      <c r="F2" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="64"/>
-      <c r="H2" s="69">
+      <c r="G2" s="49"/>
+      <c r="H2" s="52">
         <v>46230</v>
       </c>
-      <c r="I2" s="71" t="s">
+      <c r="I2" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="72"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="73"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="56"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="89"/>
-      <c r="B4" s="90"/>
-      <c r="C4" s="91"/>
-      <c r="D4" s="92"/>
-      <c r="E4" s="91"/>
-      <c r="F4" s="92"/>
-      <c r="G4" s="91"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="84"/>
+      <c r="A4" s="108"/>
+      <c r="B4" s="109"/>
+      <c r="C4" s="110"/>
+      <c r="D4" s="111"/>
+      <c r="E4" s="110"/>
+      <c r="F4" s="111"/>
+      <c r="G4" s="110"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
+      <c r="J4" s="102"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7204,19 +7572,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="52" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="51"/>
-      <c r="F1" s="52" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="51"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -7228,48 +7596,48 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="63" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="64"/>
-      <c r="F2" s="63" t="s">
+      <c r="E2" s="49"/>
+      <c r="F2" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="64"/>
-      <c r="H2" s="69">
+      <c r="G2" s="49"/>
+      <c r="H2" s="52">
         <v>46231</v>
       </c>
-      <c r="I2" s="71" t="s">
+      <c r="I2" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="72"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="73"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="56"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="99"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="73"/>
+      <c r="A4" s="60"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="56"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="34"/>
@@ -8667,7 +9035,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J1000"/>
+  <dimension ref="A1:J1005"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" customWidth="1"/>
@@ -8676,19 +9044,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="76"/>
-      <c r="D1" s="52" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="59"/>
+      <c r="D1" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="51"/>
-      <c r="F1" s="52" t="s">
+      <c r="E1" s="66"/>
+      <c r="F1" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="51"/>
+      <c r="G1" s="66"/>
       <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
@@ -8700,203 +9068,203 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="63" t="s">
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="64"/>
-      <c r="F2" s="63" t="s">
+      <c r="E2" s="49"/>
+      <c r="F2" s="48" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="64"/>
-      <c r="H2" s="69">
+      <c r="G2" s="49"/>
+      <c r="H2" s="52">
         <v>46230</v>
       </c>
-      <c r="I2" s="71" t="s">
+      <c r="I2" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="72"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="65"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="65"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="70"/>
-      <c r="I3" s="70"/>
-      <c r="J3" s="73"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="56"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="65"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="65"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
-      <c r="J4" s="73"/>
+      <c r="A4" s="60"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="56"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="110" t="s">
+      <c r="A5" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="111"/>
-      <c r="C5" s="112"/>
-      <c r="D5" s="113" t="s">
+      <c r="B5" s="63"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="72" t="s">
         <v>71</v>
       </c>
-      <c r="E5" s="111"/>
-      <c r="F5" s="111"/>
-      <c r="G5" s="111"/>
-      <c r="H5" s="111"/>
-      <c r="I5" s="111"/>
-      <c r="J5" s="114"/>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
+      <c r="G5" s="63"/>
+      <c r="H5" s="63"/>
+      <c r="I5" s="63"/>
+      <c r="J5" s="73"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="115" t="s">
+      <c r="A6" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="46"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
-      <c r="J6" s="116"/>
+      <c r="B6" s="69"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="69"/>
+      <c r="G6" s="69"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="74"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="117"/>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="57"/>
-      <c r="J7" s="118"/>
+      <c r="A7" s="75"/>
+      <c r="B7" s="76"/>
+      <c r="C7" s="76"/>
+      <c r="D7" s="76"/>
+      <c r="E7" s="76"/>
+      <c r="F7" s="76"/>
+      <c r="G7" s="76"/>
+      <c r="H7" s="76"/>
+      <c r="I7" s="76"/>
+      <c r="J7" s="77"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="119"/>
-      <c r="B8" s="120"/>
-      <c r="C8" s="120"/>
-      <c r="D8" s="120"/>
-      <c r="E8" s="120"/>
-      <c r="F8" s="120"/>
-      <c r="G8" s="120"/>
-      <c r="H8" s="120"/>
-      <c r="I8" s="120"/>
-      <c r="J8" s="121"/>
+      <c r="A8" s="78"/>
+      <c r="B8" s="61"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="79"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="119"/>
-      <c r="B9" s="120"/>
-      <c r="C9" s="120"/>
-      <c r="D9" s="120"/>
-      <c r="E9" s="120"/>
-      <c r="F9" s="120"/>
-      <c r="G9" s="120"/>
-      <c r="H9" s="120"/>
-      <c r="I9" s="120"/>
-      <c r="J9" s="121"/>
+      <c r="A9" s="78"/>
+      <c r="B9" s="61"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="61"/>
+      <c r="J9" s="79"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="119"/>
-      <c r="B10" s="120"/>
-      <c r="C10" s="120"/>
-      <c r="D10" s="120"/>
-      <c r="E10" s="120"/>
-      <c r="F10" s="120"/>
-      <c r="G10" s="120"/>
-      <c r="H10" s="120"/>
-      <c r="I10" s="120"/>
-      <c r="J10" s="121"/>
+      <c r="A10" s="78"/>
+      <c r="B10" s="61"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="61"/>
+      <c r="H10" s="61"/>
+      <c r="I10" s="61"/>
+      <c r="J10" s="79"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="119"/>
-      <c r="B11" s="120"/>
-      <c r="C11" s="120"/>
-      <c r="D11" s="120"/>
-      <c r="E11" s="120"/>
-      <c r="F11" s="120"/>
-      <c r="G11" s="120"/>
-      <c r="H11" s="120"/>
-      <c r="I11" s="120"/>
-      <c r="J11" s="121"/>
+      <c r="A11" s="78"/>
+      <c r="B11" s="61"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61"/>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="79"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="119"/>
-      <c r="B12" s="120"/>
-      <c r="C12" s="120"/>
-      <c r="D12" s="120"/>
-      <c r="E12" s="120"/>
-      <c r="F12" s="120"/>
-      <c r="G12" s="120"/>
-      <c r="H12" s="120"/>
-      <c r="I12" s="120"/>
-      <c r="J12" s="121"/>
+      <c r="A12" s="78"/>
+      <c r="B12" s="61"/>
+      <c r="C12" s="61"/>
+      <c r="D12" s="61"/>
+      <c r="E12" s="61"/>
+      <c r="F12" s="61"/>
+      <c r="G12" s="61"/>
+      <c r="H12" s="61"/>
+      <c r="I12" s="61"/>
+      <c r="J12" s="79"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="119"/>
-      <c r="B13" s="120"/>
-      <c r="C13" s="120"/>
-      <c r="D13" s="120"/>
-      <c r="E13" s="120"/>
-      <c r="F13" s="120"/>
-      <c r="G13" s="120"/>
-      <c r="H13" s="120"/>
-      <c r="I13" s="120"/>
-      <c r="J13" s="121"/>
+      <c r="A13" s="78"/>
+      <c r="B13" s="61"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="61"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="79"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="115" t="s">
+      <c r="A14" s="68" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
-      <c r="J14" s="116"/>
+      <c r="B14" s="69"/>
+      <c r="C14" s="69"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="69"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="69"/>
+      <c r="J14" s="74"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="115" t="s">
+      <c r="A15" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="46"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="45" t="s">
-        <v>76</v>
-      </c>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="48"/>
+      <c r="B15" s="69"/>
+      <c r="C15" s="70"/>
+      <c r="D15" s="80" t="s">
+        <v>92</v>
+      </c>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69"/>
+      <c r="G15" s="69"/>
+      <c r="H15" s="70"/>
       <c r="I15" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="J15" s="122" t="s">
+      <c r="J15" s="45" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="115" t="s">
+      <c r="A16" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="B16" s="46"/>
-      <c r="C16" s="48"/>
+      <c r="B16" s="69"/>
+      <c r="C16" s="70"/>
       <c r="D16" s="14" t="s">
         <v>27</v>
       </c>
@@ -8909,20 +9277,20 @@
       <c r="G16" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="62" t="s">
+      <c r="H16" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="I16" s="46"/>
-      <c r="J16" s="116"/>
+      <c r="I16" s="69"/>
+      <c r="J16" s="74"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="123" t="s">
+      <c r="A17" s="71" t="s">
         <v>72</v>
       </c>
-      <c r="B17" s="46"/>
-      <c r="C17" s="48"/>
+      <c r="B17" s="69"/>
+      <c r="C17" s="70"/>
       <c r="D17" s="15" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="E17" s="15" t="s">
         <v>74</v>
@@ -8931,66 +9299,66 @@
         <v>68</v>
       </c>
       <c r="G17" s="16" t="s">
-        <v>79</v>
-      </c>
-      <c r="H17" s="45" t="s">
-        <v>87</v>
-      </c>
-      <c r="I17" s="46"/>
-      <c r="J17" s="116"/>
+        <v>88</v>
+      </c>
+      <c r="H17" s="80" t="s">
+        <v>89</v>
+      </c>
+      <c r="I17" s="69"/>
+      <c r="J17" s="74"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="123"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="48"/>
+      <c r="A18" s="71"/>
+      <c r="B18" s="69"/>
+      <c r="C18" s="70"/>
       <c r="D18" s="15"/>
       <c r="E18" s="15"/>
       <c r="F18" s="16"/>
       <c r="G18" s="16"/>
-      <c r="H18" s="45"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="116"/>
+      <c r="H18" s="80"/>
+      <c r="I18" s="69"/>
+      <c r="J18" s="74"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="115" t="s">
+      <c r="A19" s="68" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="46"/>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="116"/>
+      <c r="B19" s="133"/>
+      <c r="C19" s="133"/>
+      <c r="D19" s="133"/>
+      <c r="E19" s="133"/>
+      <c r="F19" s="133"/>
+      <c r="G19" s="133"/>
+      <c r="H19" s="133"/>
+      <c r="I19" s="133"/>
+      <c r="J19" s="134"/>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="115" t="s">
+      <c r="A20" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="B20" s="46"/>
-      <c r="C20" s="48"/>
-      <c r="D20" s="45" t="s">
-        <v>77</v>
-      </c>
-      <c r="E20" s="46"/>
-      <c r="F20" s="46"/>
-      <c r="G20" s="46"/>
-      <c r="H20" s="48"/>
+      <c r="B20" s="69"/>
+      <c r="C20" s="70"/>
+      <c r="D20" s="80" t="s">
+        <v>76</v>
+      </c>
+      <c r="E20" s="69"/>
+      <c r="F20" s="69"/>
+      <c r="G20" s="69"/>
+      <c r="H20" s="70"/>
       <c r="I20" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="J20" s="122" t="s">
+      <c r="J20" s="45" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="115" t="s">
+      <c r="A21" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="46"/>
-      <c r="C21" s="48"/>
+      <c r="B21" s="69"/>
+      <c r="C21" s="70"/>
       <c r="D21" s="14" t="s">
         <v>27</v>
       </c>
@@ -9003,20 +9371,20 @@
       <c r="G21" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="62" t="s">
+      <c r="H21" s="81" t="s">
         <v>17</v>
       </c>
-      <c r="I21" s="46"/>
-      <c r="J21" s="116"/>
+      <c r="I21" s="69"/>
+      <c r="J21" s="74"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="123" t="s">
-        <v>73</v>
-      </c>
-      <c r="B22" s="46"/>
-      <c r="C22" s="48"/>
+      <c r="A22" s="71" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" s="69"/>
+      <c r="C22" s="70"/>
       <c r="D22" s="15" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E22" s="15" t="s">
         <v>74</v>
@@ -9025,31 +9393,120 @@
         <v>68</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>86</v>
-      </c>
-      <c r="H22" s="45" t="s">
-        <v>88</v>
-      </c>
-      <c r="I22" s="46"/>
-      <c r="J22" s="116"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A23" s="124"/>
-      <c r="B23" s="125"/>
-      <c r="C23" s="126"/>
-      <c r="D23" s="127"/>
-      <c r="E23" s="127"/>
-      <c r="F23" s="128"/>
-      <c r="G23" s="128"/>
-      <c r="H23" s="129"/>
-      <c r="I23" s="125"/>
-      <c r="J23" s="130"/>
-    </row>
-    <row r="24" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="25" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
-    <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
+        <v>79</v>
+      </c>
+      <c r="H22" s="80" t="s">
+        <v>90</v>
+      </c>
+      <c r="I22" s="69"/>
+      <c r="J22" s="74"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A23" s="71"/>
+      <c r="B23" s="69"/>
+      <c r="C23" s="70"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="80"/>
+      <c r="I23" s="69"/>
+      <c r="J23" s="74"/>
+    </row>
+    <row r="24" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A24" s="68" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="133"/>
+      <c r="C24" s="133"/>
+      <c r="D24" s="133"/>
+      <c r="E24" s="133"/>
+      <c r="F24" s="133"/>
+      <c r="G24" s="133"/>
+      <c r="H24" s="133"/>
+      <c r="I24" s="133"/>
+      <c r="J24" s="134"/>
+    </row>
+    <row r="25" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A25" s="68" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" s="133"/>
+      <c r="C25" s="138"/>
+      <c r="D25" s="80" t="s">
+        <v>77</v>
+      </c>
+      <c r="E25" s="131"/>
+      <c r="F25" s="131"/>
+      <c r="G25" s="131"/>
+      <c r="H25" s="135"/>
+      <c r="I25" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J25" s="45" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A26" s="68" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="133"/>
+      <c r="C26" s="138"/>
+      <c r="D26" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E26" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F26" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="G26" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="H26" s="81" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="133"/>
+      <c r="J26" s="134"/>
+    </row>
+    <row r="27" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A27" s="71" t="s">
+        <v>73</v>
+      </c>
+      <c r="B27" s="136"/>
+      <c r="C27" s="137"/>
+      <c r="D27" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="E27" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="G27" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="H27" s="80" t="s">
+        <v>91</v>
+      </c>
+      <c r="I27" s="131"/>
+      <c r="J27" s="132"/>
+    </row>
+    <row r="28" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A28" s="67"/>
+      <c r="B28" s="129"/>
+      <c r="C28" s="130"/>
+      <c r="D28" s="46"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="47"/>
+      <c r="G28" s="47"/>
+      <c r="H28" s="82"/>
+      <c r="I28" s="127"/>
+      <c r="J28" s="128"/>
+    </row>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="30" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="31" spans="1:10" ht="12.75" customHeight="1"/>
@@ -10022,13 +10479,31 @@
     <row r="998" ht="12.75" customHeight="1"/>
     <row r="999" ht="12.75" customHeight="1"/>
     <row r="1000" ht="12.75" customHeight="1"/>
+    <row r="1001" ht="12.75" customHeight="1"/>
+    <row r="1002" ht="12.75" customHeight="1"/>
+    <row r="1003" ht="12.75" customHeight="1"/>
+    <row r="1004" ht="12.75" customHeight="1"/>
+    <row r="1005" ht="12.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="A1:C4"/>
+  <mergeCells count="39">
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="H27:J27"/>
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="H28:J28"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="H18:J18"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H22:J22"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
@@ -10045,15 +10520,11 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D2:E4"/>
     <mergeCell ref="H23:J23"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="A1:C4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10073,182 +10544,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="107" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="52" t="s">
+      <c r="B1" s="58"/>
+      <c r="C1" s="58"/>
+      <c r="D1" s="58"/>
+      <c r="E1" s="58"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="52" t="s">
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="66"/>
+      <c r="K1" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="50"/>
-      <c r="M1" s="50"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="52" t="s">
+      <c r="L1" s="104"/>
+      <c r="M1" s="104"/>
+      <c r="N1" s="66"/>
+      <c r="O1" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="52" t="s">
+      <c r="P1" s="66"/>
+      <c r="Q1" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="R1" s="51"/>
-      <c r="S1" s="52" t="s">
+      <c r="R1" s="66"/>
+      <c r="S1" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="T1" s="56"/>
+      <c r="T1" s="106"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="59"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
-      <c r="D2" s="60"/>
-      <c r="E2" s="60"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="63"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="63"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="64"/>
-      <c r="O2" s="63"/>
-      <c r="P2" s="64"/>
-      <c r="Q2" s="63"/>
-      <c r="R2" s="64"/>
-      <c r="S2" s="63"/>
-      <c r="T2" s="58"/>
+      <c r="A2" s="60"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="76"/>
+      <c r="M2" s="76"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="48"/>
+      <c r="P2" s="49"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="49"/>
+      <c r="S2" s="48"/>
+      <c r="T2" s="117"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="59"/>
-      <c r="B3" s="60"/>
-      <c r="C3" s="60"/>
-      <c r="D3" s="60"/>
-      <c r="E3" s="60"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="65"/>
-      <c r="H3" s="60"/>
-      <c r="I3" s="60"/>
-      <c r="J3" s="66"/>
-      <c r="K3" s="65"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="60"/>
-      <c r="N3" s="66"/>
-      <c r="O3" s="65"/>
-      <c r="P3" s="66"/>
-      <c r="Q3" s="65"/>
-      <c r="R3" s="66"/>
-      <c r="S3" s="65"/>
-      <c r="T3" s="61"/>
+      <c r="A3" s="60"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="61"/>
+      <c r="D3" s="61"/>
+      <c r="E3" s="61"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="61"/>
+      <c r="I3" s="61"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="50"/>
+      <c r="L3" s="61"/>
+      <c r="M3" s="61"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="50"/>
+      <c r="P3" s="51"/>
+      <c r="Q3" s="50"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="50"/>
+      <c r="T3" s="118"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="89"/>
-      <c r="B4" s="90"/>
-      <c r="C4" s="90"/>
-      <c r="D4" s="90"/>
-      <c r="E4" s="90"/>
-      <c r="F4" s="91"/>
-      <c r="G4" s="92"/>
-      <c r="H4" s="90"/>
-      <c r="I4" s="90"/>
-      <c r="J4" s="91"/>
-      <c r="K4" s="92"/>
-      <c r="L4" s="90"/>
-      <c r="M4" s="90"/>
-      <c r="N4" s="91"/>
-      <c r="O4" s="92"/>
-      <c r="P4" s="91"/>
-      <c r="Q4" s="92"/>
-      <c r="R4" s="91"/>
-      <c r="S4" s="92"/>
-      <c r="T4" s="108"/>
+      <c r="A4" s="108"/>
+      <c r="B4" s="109"/>
+      <c r="C4" s="109"/>
+      <c r="D4" s="109"/>
+      <c r="E4" s="109"/>
+      <c r="F4" s="110"/>
+      <c r="G4" s="111"/>
+      <c r="H4" s="109"/>
+      <c r="I4" s="109"/>
+      <c r="J4" s="110"/>
+      <c r="K4" s="111"/>
+      <c r="L4" s="109"/>
+      <c r="M4" s="109"/>
+      <c r="N4" s="110"/>
+      <c r="O4" s="111"/>
+      <c r="P4" s="110"/>
+      <c r="Q4" s="111"/>
+      <c r="R4" s="110"/>
+      <c r="S4" s="111"/>
+      <c r="T4" s="119"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="49" t="s">
+      <c r="A5" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="86" t="s">
+      <c r="B5" s="104"/>
+      <c r="C5" s="104"/>
+      <c r="D5" s="104"/>
+      <c r="E5" s="104"/>
+      <c r="F5" s="66"/>
+      <c r="G5" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="50"/>
-      <c r="N5" s="50"/>
-      <c r="O5" s="50"/>
-      <c r="P5" s="50"/>
-      <c r="Q5" s="50"/>
-      <c r="R5" s="50"/>
-      <c r="S5" s="50"/>
-      <c r="T5" s="56"/>
+      <c r="H5" s="104"/>
+      <c r="I5" s="104"/>
+      <c r="J5" s="104"/>
+      <c r="K5" s="104"/>
+      <c r="L5" s="104"/>
+      <c r="M5" s="104"/>
+      <c r="N5" s="104"/>
+      <c r="O5" s="104"/>
+      <c r="P5" s="104"/>
+      <c r="Q5" s="104"/>
+      <c r="R5" s="104"/>
+      <c r="S5" s="104"/>
+      <c r="T5" s="106"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="55" t="s">
+      <c r="A6" s="121" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="46"/>
-      <c r="C6" s="46"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="45" t="s">
+      <c r="B6" s="69"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
+      <c r="E6" s="69"/>
+      <c r="F6" s="70"/>
+      <c r="G6" s="80" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
-      <c r="L6" s="46"/>
-      <c r="M6" s="46"/>
-      <c r="N6" s="46"/>
-      <c r="O6" s="46"/>
-      <c r="P6" s="46"/>
-      <c r="Q6" s="46"/>
-      <c r="R6" s="46"/>
-      <c r="S6" s="46"/>
-      <c r="T6" s="47"/>
+      <c r="H6" s="69"/>
+      <c r="I6" s="69"/>
+      <c r="J6" s="69"/>
+      <c r="K6" s="69"/>
+      <c r="L6" s="69"/>
+      <c r="M6" s="69"/>
+      <c r="N6" s="69"/>
+      <c r="O6" s="69"/>
+      <c r="P6" s="69"/>
+      <c r="Q6" s="69"/>
+      <c r="R6" s="69"/>
+      <c r="S6" s="69"/>
+      <c r="T6" s="91"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="121" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="46"/>
-      <c r="C7" s="46"/>
-      <c r="D7" s="46"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="45" t="s">
+      <c r="B7" s="69"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
+      <c r="E7" s="69"/>
+      <c r="F7" s="70"/>
+      <c r="G7" s="80" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="46"/>
-      <c r="I7" s="46"/>
-      <c r="J7" s="46"/>
-      <c r="K7" s="46"/>
-      <c r="L7" s="46"/>
-      <c r="M7" s="46"/>
-      <c r="N7" s="46"/>
-      <c r="O7" s="46"/>
-      <c r="P7" s="46"/>
-      <c r="Q7" s="46"/>
-      <c r="R7" s="46"/>
-      <c r="S7" s="46"/>
-      <c r="T7" s="47"/>
+      <c r="H7" s="69"/>
+      <c r="I7" s="69"/>
+      <c r="J7" s="69"/>
+      <c r="K7" s="69"/>
+      <c r="L7" s="69"/>
+      <c r="M7" s="69"/>
+      <c r="N7" s="69"/>
+      <c r="O7" s="69"/>
+      <c r="P7" s="69"/>
+      <c r="Q7" s="69"/>
+      <c r="R7" s="69"/>
+      <c r="S7" s="69"/>
+      <c r="T7" s="91"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -10447,37 +10918,37 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="55" t="s">
+      <c r="A15" s="121" t="s">
         <v>43</v>
       </c>
-      <c r="B15" s="48"/>
-      <c r="C15" s="107" t="s">
+      <c r="B15" s="70"/>
+      <c r="C15" s="124" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="48"/>
-      <c r="E15" s="62" t="s">
+      <c r="D15" s="70"/>
+      <c r="E15" s="81" t="s">
         <v>44</v>
       </c>
-      <c r="F15" s="48"/>
-      <c r="G15" s="62" t="s">
+      <c r="F15" s="70"/>
+      <c r="G15" s="81" t="s">
         <v>45</v>
       </c>
-      <c r="H15" s="46"/>
-      <c r="I15" s="48"/>
-      <c r="J15" s="62" t="s">
+      <c r="H15" s="69"/>
+      <c r="I15" s="70"/>
+      <c r="J15" s="81" t="s">
         <v>46</v>
       </c>
-      <c r="K15" s="48"/>
-      <c r="L15" s="62" t="s">
+      <c r="K15" s="70"/>
+      <c r="L15" s="81" t="s">
         <v>47</v>
       </c>
-      <c r="M15" s="46"/>
-      <c r="N15" s="48"/>
-      <c r="O15" s="62" t="s">
+      <c r="M15" s="69"/>
+      <c r="N15" s="70"/>
+      <c r="O15" s="81" t="s">
         <v>48</v>
       </c>
-      <c r="P15" s="46"/>
-      <c r="Q15" s="48"/>
+      <c r="P15" s="69"/>
+      <c r="Q15" s="70"/>
       <c r="R15" s="14" t="s">
         <v>49</v>
       </c>
@@ -10489,37 +10960,37 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="100">
+      <c r="A16" s="122">
         <v>1</v>
       </c>
-      <c r="B16" s="48"/>
-      <c r="C16" s="101" t="s">
+      <c r="B16" s="70"/>
+      <c r="C16" s="123" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="48"/>
-      <c r="E16" s="101" t="s">
+      <c r="D16" s="70"/>
+      <c r="E16" s="123" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="48"/>
-      <c r="G16" s="106" t="s">
+      <c r="F16" s="70"/>
+      <c r="G16" s="113" t="s">
         <v>54</v>
       </c>
-      <c r="H16" s="46"/>
-      <c r="I16" s="48"/>
-      <c r="J16" s="106" t="s">
+      <c r="H16" s="69"/>
+      <c r="I16" s="70"/>
+      <c r="J16" s="113" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="48"/>
-      <c r="L16" s="104" t="s">
+      <c r="K16" s="70"/>
+      <c r="L16" s="115" t="s">
         <v>56</v>
       </c>
-      <c r="M16" s="46"/>
-      <c r="N16" s="48"/>
-      <c r="O16" s="104" t="s">
+      <c r="M16" s="69"/>
+      <c r="N16" s="70"/>
+      <c r="O16" s="115" t="s">
         <v>57</v>
       </c>
-      <c r="P16" s="46"/>
-      <c r="Q16" s="48"/>
+      <c r="P16" s="69"/>
+      <c r="Q16" s="70"/>
       <c r="R16" s="29"/>
       <c r="S16" s="29"/>
       <c r="T16" s="30"/>
@@ -10531,37 +11002,37 @@
       <c r="Z16" s="31"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="100">
+      <c r="A17" s="122">
         <v>2</v>
       </c>
-      <c r="B17" s="48"/>
-      <c r="C17" s="101" t="s">
+      <c r="B17" s="70"/>
+      <c r="C17" s="123" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="48"/>
-      <c r="E17" s="101" t="s">
+      <c r="D17" s="70"/>
+      <c r="E17" s="123" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="48"/>
-      <c r="G17" s="106" t="s">
+      <c r="F17" s="70"/>
+      <c r="G17" s="113" t="s">
         <v>60</v>
       </c>
-      <c r="H17" s="46"/>
-      <c r="I17" s="48"/>
-      <c r="J17" s="106" t="s">
+      <c r="H17" s="69"/>
+      <c r="I17" s="70"/>
+      <c r="J17" s="113" t="s">
         <v>61</v>
       </c>
-      <c r="K17" s="48"/>
-      <c r="L17" s="104" t="s">
+      <c r="K17" s="70"/>
+      <c r="L17" s="115" t="s">
         <v>62</v>
       </c>
-      <c r="M17" s="46"/>
-      <c r="N17" s="48"/>
-      <c r="O17" s="104" t="s">
+      <c r="M17" s="69"/>
+      <c r="N17" s="70"/>
+      <c r="O17" s="115" t="s">
         <v>63</v>
       </c>
-      <c r="P17" s="46"/>
-      <c r="Q17" s="48"/>
+      <c r="P17" s="69"/>
+      <c r="Q17" s="70"/>
       <c r="R17" s="29"/>
       <c r="S17" s="29"/>
       <c r="T17" s="30"/>
@@ -10573,23 +11044,23 @@
       <c r="Z17" s="31"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="100"/>
-      <c r="B18" s="48"/>
-      <c r="C18" s="101"/>
-      <c r="D18" s="48"/>
-      <c r="E18" s="101"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="106"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="48"/>
-      <c r="J18" s="106"/>
-      <c r="K18" s="48"/>
-      <c r="L18" s="104"/>
-      <c r="M18" s="46"/>
-      <c r="N18" s="48"/>
-      <c r="O18" s="104"/>
-      <c r="P18" s="46"/>
-      <c r="Q18" s="48"/>
+      <c r="A18" s="122"/>
+      <c r="B18" s="70"/>
+      <c r="C18" s="123"/>
+      <c r="D18" s="70"/>
+      <c r="E18" s="123"/>
+      <c r="F18" s="70"/>
+      <c r="G18" s="113"/>
+      <c r="H18" s="69"/>
+      <c r="I18" s="70"/>
+      <c r="J18" s="113"/>
+      <c r="K18" s="70"/>
+      <c r="L18" s="115"/>
+      <c r="M18" s="69"/>
+      <c r="N18" s="70"/>
+      <c r="O18" s="115"/>
+      <c r="P18" s="69"/>
+      <c r="Q18" s="70"/>
       <c r="R18" s="29"/>
       <c r="S18" s="29"/>
       <c r="T18" s="30"/>
@@ -10601,23 +11072,23 @@
       <c r="Z18" s="31"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="100"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="101"/>
-      <c r="D19" s="48"/>
-      <c r="E19" s="101"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="106"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="48"/>
-      <c r="J19" s="106"/>
-      <c r="K19" s="48"/>
-      <c r="L19" s="104"/>
-      <c r="M19" s="46"/>
-      <c r="N19" s="48"/>
-      <c r="O19" s="104"/>
-      <c r="P19" s="46"/>
-      <c r="Q19" s="48"/>
+      <c r="A19" s="122"/>
+      <c r="B19" s="70"/>
+      <c r="C19" s="123"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="123"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="113"/>
+      <c r="H19" s="69"/>
+      <c r="I19" s="70"/>
+      <c r="J19" s="113"/>
+      <c r="K19" s="70"/>
+      <c r="L19" s="115"/>
+      <c r="M19" s="69"/>
+      <c r="N19" s="70"/>
+      <c r="O19" s="115"/>
+      <c r="P19" s="69"/>
+      <c r="Q19" s="70"/>
       <c r="R19" s="29"/>
       <c r="S19" s="29"/>
       <c r="T19" s="30"/>
@@ -10629,23 +11100,23 @@
       <c r="Z19" s="31"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="100"/>
-      <c r="B20" s="48"/>
-      <c r="C20" s="101"/>
-      <c r="D20" s="48"/>
-      <c r="E20" s="101"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="106"/>
-      <c r="H20" s="46"/>
-      <c r="I20" s="48"/>
-      <c r="J20" s="106"/>
-      <c r="K20" s="48"/>
-      <c r="L20" s="104"/>
-      <c r="M20" s="46"/>
-      <c r="N20" s="48"/>
-      <c r="O20" s="104"/>
-      <c r="P20" s="46"/>
-      <c r="Q20" s="48"/>
+      <c r="A20" s="122"/>
+      <c r="B20" s="70"/>
+      <c r="C20" s="123"/>
+      <c r="D20" s="70"/>
+      <c r="E20" s="123"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="113"/>
+      <c r="H20" s="69"/>
+      <c r="I20" s="70"/>
+      <c r="J20" s="113"/>
+      <c r="K20" s="70"/>
+      <c r="L20" s="115"/>
+      <c r="M20" s="69"/>
+      <c r="N20" s="70"/>
+      <c r="O20" s="115"/>
+      <c r="P20" s="69"/>
+      <c r="Q20" s="70"/>
       <c r="R20" s="29"/>
       <c r="S20" s="29"/>
       <c r="T20" s="30"/>
@@ -10657,23 +11128,23 @@
       <c r="Z20" s="31"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="100"/>
-      <c r="B21" s="48"/>
-      <c r="C21" s="101"/>
-      <c r="D21" s="48"/>
-      <c r="E21" s="101"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="106"/>
-      <c r="H21" s="46"/>
-      <c r="I21" s="48"/>
-      <c r="J21" s="106"/>
-      <c r="K21" s="48"/>
-      <c r="L21" s="104"/>
-      <c r="M21" s="46"/>
-      <c r="N21" s="48"/>
-      <c r="O21" s="104"/>
-      <c r="P21" s="46"/>
-      <c r="Q21" s="48"/>
+      <c r="A21" s="122"/>
+      <c r="B21" s="70"/>
+      <c r="C21" s="123"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="123"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="113"/>
+      <c r="H21" s="69"/>
+      <c r="I21" s="70"/>
+      <c r="J21" s="113"/>
+      <c r="K21" s="70"/>
+      <c r="L21" s="115"/>
+      <c r="M21" s="69"/>
+      <c r="N21" s="70"/>
+      <c r="O21" s="115"/>
+      <c r="P21" s="69"/>
+      <c r="Q21" s="70"/>
       <c r="R21" s="29"/>
       <c r="S21" s="29"/>
       <c r="T21" s="30"/>
@@ -10685,23 +11156,23 @@
       <c r="Z21" s="31"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="100"/>
-      <c r="B22" s="48"/>
-      <c r="C22" s="101"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="101"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="106"/>
-      <c r="H22" s="46"/>
-      <c r="I22" s="48"/>
-      <c r="J22" s="106"/>
-      <c r="K22" s="48"/>
-      <c r="L22" s="104"/>
-      <c r="M22" s="46"/>
-      <c r="N22" s="48"/>
-      <c r="O22" s="104"/>
-      <c r="P22" s="46"/>
-      <c r="Q22" s="48"/>
+      <c r="A22" s="122"/>
+      <c r="B22" s="70"/>
+      <c r="C22" s="123"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="123"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="113"/>
+      <c r="H22" s="69"/>
+      <c r="I22" s="70"/>
+      <c r="J22" s="113"/>
+      <c r="K22" s="70"/>
+      <c r="L22" s="115"/>
+      <c r="M22" s="69"/>
+      <c r="N22" s="70"/>
+      <c r="O22" s="115"/>
+      <c r="P22" s="69"/>
+      <c r="Q22" s="70"/>
       <c r="R22" s="29"/>
       <c r="S22" s="29"/>
       <c r="T22" s="30"/>
@@ -10713,23 +11184,23 @@
       <c r="Z22" s="31"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="100"/>
-      <c r="B23" s="48"/>
-      <c r="C23" s="101"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="101"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="106"/>
-      <c r="H23" s="46"/>
-      <c r="I23" s="48"/>
-      <c r="J23" s="106"/>
-      <c r="K23" s="48"/>
-      <c r="L23" s="104"/>
-      <c r="M23" s="46"/>
-      <c r="N23" s="48"/>
-      <c r="O23" s="104"/>
-      <c r="P23" s="46"/>
-      <c r="Q23" s="48"/>
+      <c r="A23" s="122"/>
+      <c r="B23" s="70"/>
+      <c r="C23" s="123"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="123"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="113"/>
+      <c r="H23" s="69"/>
+      <c r="I23" s="70"/>
+      <c r="J23" s="113"/>
+      <c r="K23" s="70"/>
+      <c r="L23" s="115"/>
+      <c r="M23" s="69"/>
+      <c r="N23" s="70"/>
+      <c r="O23" s="115"/>
+      <c r="P23" s="69"/>
+      <c r="Q23" s="70"/>
       <c r="R23" s="29"/>
       <c r="S23" s="29"/>
       <c r="T23" s="30"/>
@@ -10741,23 +11212,23 @@
       <c r="Z23" s="31"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="100"/>
-      <c r="B24" s="48"/>
-      <c r="C24" s="101"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="101"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="106"/>
-      <c r="H24" s="46"/>
-      <c r="I24" s="48"/>
-      <c r="J24" s="106"/>
-      <c r="K24" s="48"/>
-      <c r="L24" s="104"/>
-      <c r="M24" s="46"/>
-      <c r="N24" s="48"/>
-      <c r="O24" s="104"/>
-      <c r="P24" s="46"/>
-      <c r="Q24" s="48"/>
+      <c r="A24" s="122"/>
+      <c r="B24" s="70"/>
+      <c r="C24" s="123"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="123"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="113"/>
+      <c r="H24" s="69"/>
+      <c r="I24" s="70"/>
+      <c r="J24" s="113"/>
+      <c r="K24" s="70"/>
+      <c r="L24" s="115"/>
+      <c r="M24" s="69"/>
+      <c r="N24" s="70"/>
+      <c r="O24" s="115"/>
+      <c r="P24" s="69"/>
+      <c r="Q24" s="70"/>
       <c r="R24" s="29"/>
       <c r="S24" s="29"/>
       <c r="T24" s="30"/>
@@ -10769,23 +11240,23 @@
       <c r="Z24" s="31"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="100"/>
-      <c r="B25" s="48"/>
-      <c r="C25" s="101"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="101"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="106"/>
-      <c r="H25" s="46"/>
-      <c r="I25" s="48"/>
-      <c r="J25" s="106"/>
-      <c r="K25" s="48"/>
-      <c r="L25" s="104"/>
-      <c r="M25" s="46"/>
-      <c r="N25" s="48"/>
-      <c r="O25" s="104"/>
-      <c r="P25" s="46"/>
-      <c r="Q25" s="48"/>
+      <c r="A25" s="122"/>
+      <c r="B25" s="70"/>
+      <c r="C25" s="123"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="123"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="113"/>
+      <c r="H25" s="69"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="113"/>
+      <c r="K25" s="70"/>
+      <c r="L25" s="115"/>
+      <c r="M25" s="69"/>
+      <c r="N25" s="70"/>
+      <c r="O25" s="115"/>
+      <c r="P25" s="69"/>
+      <c r="Q25" s="70"/>
       <c r="R25" s="29"/>
       <c r="S25" s="29"/>
       <c r="T25" s="30"/>
@@ -10797,23 +11268,23 @@
       <c r="Z25" s="31"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="100"/>
-      <c r="B26" s="48"/>
-      <c r="C26" s="101"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="101"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="106"/>
-      <c r="H26" s="46"/>
-      <c r="I26" s="48"/>
-      <c r="J26" s="106"/>
-      <c r="K26" s="48"/>
-      <c r="L26" s="104"/>
-      <c r="M26" s="46"/>
-      <c r="N26" s="48"/>
-      <c r="O26" s="104"/>
-      <c r="P26" s="46"/>
-      <c r="Q26" s="48"/>
+      <c r="A26" s="122"/>
+      <c r="B26" s="70"/>
+      <c r="C26" s="123"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="123"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="113"/>
+      <c r="H26" s="69"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="113"/>
+      <c r="K26" s="70"/>
+      <c r="L26" s="115"/>
+      <c r="M26" s="69"/>
+      <c r="N26" s="70"/>
+      <c r="O26" s="115"/>
+      <c r="P26" s="69"/>
+      <c r="Q26" s="70"/>
       <c r="R26" s="29"/>
       <c r="S26" s="29"/>
       <c r="T26" s="30"/>
@@ -10825,23 +11296,23 @@
       <c r="Z26" s="31"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="100"/>
-      <c r="B27" s="48"/>
-      <c r="C27" s="101"/>
-      <c r="D27" s="48"/>
-      <c r="E27" s="101"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="106"/>
-      <c r="H27" s="46"/>
-      <c r="I27" s="48"/>
-      <c r="J27" s="106"/>
-      <c r="K27" s="48"/>
-      <c r="L27" s="104"/>
-      <c r="M27" s="46"/>
-      <c r="N27" s="48"/>
-      <c r="O27" s="104"/>
-      <c r="P27" s="46"/>
-      <c r="Q27" s="48"/>
+      <c r="A27" s="122"/>
+      <c r="B27" s="70"/>
+      <c r="C27" s="123"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="123"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="113"/>
+      <c r="H27" s="69"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="113"/>
+      <c r="K27" s="70"/>
+      <c r="L27" s="115"/>
+      <c r="M27" s="69"/>
+      <c r="N27" s="70"/>
+      <c r="O27" s="115"/>
+      <c r="P27" s="69"/>
+      <c r="Q27" s="70"/>
       <c r="R27" s="29"/>
       <c r="S27" s="29"/>
       <c r="T27" s="30"/>
@@ -10853,23 +11324,23 @@
       <c r="Z27" s="31"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="100"/>
-      <c r="B28" s="48"/>
-      <c r="C28" s="101"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="101"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="106"/>
-      <c r="H28" s="46"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="106"/>
-      <c r="K28" s="48"/>
-      <c r="L28" s="104"/>
-      <c r="M28" s="46"/>
-      <c r="N28" s="48"/>
-      <c r="O28" s="104"/>
-      <c r="P28" s="46"/>
-      <c r="Q28" s="48"/>
+      <c r="A28" s="122"/>
+      <c r="B28" s="70"/>
+      <c r="C28" s="123"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="123"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="113"/>
+      <c r="H28" s="69"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="113"/>
+      <c r="K28" s="70"/>
+      <c r="L28" s="115"/>
+      <c r="M28" s="69"/>
+      <c r="N28" s="70"/>
+      <c r="O28" s="115"/>
+      <c r="P28" s="69"/>
+      <c r="Q28" s="70"/>
       <c r="R28" s="29"/>
       <c r="S28" s="29"/>
       <c r="T28" s="30"/>
@@ -10881,23 +11352,23 @@
       <c r="Z28" s="31"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="100"/>
-      <c r="B29" s="48"/>
-      <c r="C29" s="101"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="101"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="106"/>
-      <c r="H29" s="46"/>
-      <c r="I29" s="48"/>
-      <c r="J29" s="106"/>
-      <c r="K29" s="48"/>
-      <c r="L29" s="104"/>
-      <c r="M29" s="46"/>
-      <c r="N29" s="48"/>
-      <c r="O29" s="104"/>
-      <c r="P29" s="46"/>
-      <c r="Q29" s="48"/>
+      <c r="A29" s="122"/>
+      <c r="B29" s="70"/>
+      <c r="C29" s="123"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="123"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="113"/>
+      <c r="H29" s="69"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="113"/>
+      <c r="K29" s="70"/>
+      <c r="L29" s="115"/>
+      <c r="M29" s="69"/>
+      <c r="N29" s="70"/>
+      <c r="O29" s="115"/>
+      <c r="P29" s="69"/>
+      <c r="Q29" s="70"/>
       <c r="R29" s="29"/>
       <c r="S29" s="29"/>
       <c r="T29" s="30"/>
@@ -10909,23 +11380,23 @@
       <c r="Z29" s="31"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="100"/>
-      <c r="B30" s="48"/>
-      <c r="C30" s="101"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="101"/>
-      <c r="F30" s="48"/>
-      <c r="G30" s="106"/>
-      <c r="H30" s="46"/>
-      <c r="I30" s="48"/>
-      <c r="J30" s="106"/>
-      <c r="K30" s="48"/>
-      <c r="L30" s="104"/>
-      <c r="M30" s="46"/>
-      <c r="N30" s="48"/>
-      <c r="O30" s="104"/>
-      <c r="P30" s="46"/>
-      <c r="Q30" s="48"/>
+      <c r="A30" s="122"/>
+      <c r="B30" s="70"/>
+      <c r="C30" s="123"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="123"/>
+      <c r="F30" s="70"/>
+      <c r="G30" s="113"/>
+      <c r="H30" s="69"/>
+      <c r="I30" s="70"/>
+      <c r="J30" s="113"/>
+      <c r="K30" s="70"/>
+      <c r="L30" s="115"/>
+      <c r="M30" s="69"/>
+      <c r="N30" s="70"/>
+      <c r="O30" s="115"/>
+      <c r="P30" s="69"/>
+      <c r="Q30" s="70"/>
       <c r="R30" s="29"/>
       <c r="S30" s="29"/>
       <c r="T30" s="30"/>
@@ -10937,23 +11408,23 @@
       <c r="Z30" s="31"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="102"/>
-      <c r="B31" s="54"/>
-      <c r="C31" s="103"/>
-      <c r="D31" s="54"/>
-      <c r="E31" s="103"/>
-      <c r="F31" s="54"/>
-      <c r="G31" s="109"/>
-      <c r="H31" s="53"/>
-      <c r="I31" s="54"/>
-      <c r="J31" s="109"/>
-      <c r="K31" s="54"/>
-      <c r="L31" s="105"/>
-      <c r="M31" s="53"/>
-      <c r="N31" s="54"/>
-      <c r="O31" s="105"/>
-      <c r="P31" s="53"/>
-      <c r="Q31" s="54"/>
+      <c r="A31" s="125"/>
+      <c r="B31" s="94"/>
+      <c r="C31" s="126"/>
+      <c r="D31" s="94"/>
+      <c r="E31" s="126"/>
+      <c r="F31" s="94"/>
+      <c r="G31" s="114"/>
+      <c r="H31" s="93"/>
+      <c r="I31" s="94"/>
+      <c r="J31" s="114"/>
+      <c r="K31" s="94"/>
+      <c r="L31" s="116"/>
+      <c r="M31" s="93"/>
+      <c r="N31" s="94"/>
+      <c r="O31" s="116"/>
+      <c r="P31" s="93"/>
+      <c r="Q31" s="94"/>
       <c r="R31" s="32"/>
       <c r="S31" s="32"/>
       <c r="T31" s="33"/>
@@ -11951,62 +12422,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -12031,62 +12502,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
